--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2023_arica_y_parinacota.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:49</t>
+    <t xml:space="preserve">2026-09-24 01:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -549,10 +549,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-0.04</v>
+        <v>0.07</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3">
@@ -563,10 +563,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4">
@@ -577,10 +577,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-0.03</v>
+        <v>0.12</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5">
@@ -591,10 +591,10 @@
         <v>5</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6">
@@ -605,10 +605,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7">
@@ -619,7 +619,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>328</v>
@@ -633,7 +633,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.16</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>328</v>
@@ -647,7 +647,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.14</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>328</v>
@@ -661,7 +661,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>328</v>
@@ -689,7 +689,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>328</v>
@@ -703,7 +703,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>328</v>
@@ -717,7 +717,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>328</v>
@@ -731,7 +731,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>328</v>
@@ -745,7 +745,7 @@
         <v>11</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>328</v>
@@ -759,7 +759,7 @@
         <v>11</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.1</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>328</v>
@@ -773,10 +773,10 @@
         <v>23</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.19</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19">
@@ -787,7 +787,7 @@
         <v>25</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.65</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>328</v>
@@ -801,7 +801,7 @@
         <v>25</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.24</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>328</v>
@@ -815,10 +815,10 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22">
@@ -829,10 +829,10 @@
         <v>28</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.11</v>
+        <v>0.03</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="23">
@@ -846,7 +846,7 @@
         <v>0.14</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="24">
@@ -857,7 +857,7 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0.07</v>
+        <v>0.13</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>345</v>
@@ -871,10 +871,10 @@
         <v>28</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="26">
@@ -885,10 +885,10 @@
         <v>28</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.59</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2023_arica_y_parinacota.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:38</t>
+    <t xml:space="preserve">2026-10-01 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2023_arica_y_parinacota.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:07</t>
+    <t xml:space="preserve">2026-10-05 20:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
